--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
